--- a/R&D_Mining_Contractor_Valuation_Model.xlsx
+++ b/R&D_Mining_Contractor_Valuation_Model.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Financial Data Input" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Historical Analysis" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DCF Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Comparable Analysis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Precedent Transactions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Asset-Based Valuation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Valuation Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sensitivity Analysis" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risk Analysis" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Data Input" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparable Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precedent Transactions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset-Based Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity Analysis" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Analysis" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2473,40 +2473,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EBITDA Margin (Terminal)</t>
+          <t>Revenue Growth Rate (Years 6-10)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Capex as % of Revenue</t>
+          <t>EBITDA Margin (Terminal)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Working Capital as % of Revenue</t>
+          <t>Capex as % of Revenue</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Working Capital as % of Revenue</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Depreciation as % of Capex</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2775,7 +2785,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2806,10 +2816,210 @@
         <v>156429234.6323871</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5674268557185992</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="L19" t="n">
-        <v>88762148.74992241</v>
+        <v>79251918.52671643</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6590257403.353745</v>
+      </c>
+      <c r="C20" t="n">
+        <v>988538610.5030617</v>
+      </c>
+      <c r="D20" t="n">
+        <v>941478419.5850617</v>
+      </c>
+      <c r="E20" t="n">
+        <v>235369604.8962654</v>
+      </c>
+      <c r="F20" t="n">
+        <v>706108814.6887963</v>
+      </c>
+      <c r="G20" t="n">
+        <v>47060190.91800001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>527220592.2682996</v>
+      </c>
+      <c r="I20" t="n">
+        <v>65902574.03353745</v>
+      </c>
+      <c r="J20" t="n">
+        <v>160045839.3049592</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.4523492153368934</v>
+      </c>
+      <c r="L20" t="n">
+        <v>72396609.82753284</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6755013838.437587</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1013252075.765638</v>
+      </c>
+      <c r="D21" t="n">
+        <v>966191884.847638</v>
+      </c>
+      <c r="E21" t="n">
+        <v>241547971.2119095</v>
+      </c>
+      <c r="F21" t="n">
+        <v>724643913.6357285</v>
+      </c>
+      <c r="G21" t="n">
+        <v>47060190.91800001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>540401107.075007</v>
+      </c>
+      <c r="I21" t="n">
+        <v>67550138.38437587</v>
+      </c>
+      <c r="J21" t="n">
+        <v>163752859.0943456</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.403883227979369</v>
+      </c>
+      <c r="L21" t="n">
+        <v>66137033.32187509</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6923889184.398525</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1038583377.659779</v>
+      </c>
+      <c r="D22" t="n">
+        <v>991523186.7417787</v>
+      </c>
+      <c r="E22" t="n">
+        <v>247880796.6854447</v>
+      </c>
+      <c r="F22" t="n">
+        <v>743642390.056334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>47060190.91800001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>553911134.7518821</v>
+      </c>
+      <c r="I22" t="n">
+        <v>69238891.84398526</v>
+      </c>
+      <c r="J22" t="n">
+        <v>167552554.3784667</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3606100249815795</v>
+      </c>
+      <c r="L22" t="n">
+        <v>60421130.82014631</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7096986414.008488</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1064547962.101273</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1017487771.183273</v>
+      </c>
+      <c r="E23" t="n">
+        <v>254371942.7958183</v>
+      </c>
+      <c r="F23" t="n">
+        <v>763115828.3874547</v>
+      </c>
+      <c r="G23" t="n">
+        <v>47060190.91800001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>567758913.120679</v>
+      </c>
+      <c r="I23" t="n">
+        <v>70969864.14008489</v>
+      </c>
+      <c r="J23" t="n">
+        <v>171447242.0446908</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.3219732365906959</v>
+      </c>
+      <c r="L23" t="n">
+        <v>55201423.42567755</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7274411074.358699</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1091161661.153805</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1044101470.235805</v>
+      </c>
+      <c r="E24" t="n">
+        <v>261025367.5589512</v>
+      </c>
+      <c r="F24" t="n">
+        <v>783076102.6768537</v>
+      </c>
+      <c r="G24" t="n">
+        <v>47060190.91800001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>581952885.9486959</v>
+      </c>
+      <c r="I24" t="n">
+        <v>72744110.743587</v>
+      </c>
+      <c r="J24" t="n">
+        <v>175439296.9025707</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3219732365906959</v>
+      </c>
+      <c r="L24" t="n">
+        <v>56486758.24891675</v>
       </c>
     </row>
     <row r="26">
@@ -2827,11 +3037,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sum of PV of FCF (2025-2029)</t>
+          <t>Sum of PV of FCF (2025-2034)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>513008503.6410141</v>
+        <v>846416619.5629623</v>
       </c>
     </row>
     <row r="28">
@@ -2841,7 +3051,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1646623522.44618</v>
+        <v>1846729441.079692</v>
       </c>
     </row>
     <row r="29">
@@ -2851,7 +3061,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>934338407.8939202</v>
+        <v>594597455.2517552</v>
       </c>
     </row>
     <row r="30">
@@ -2861,7 +3071,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1447346911.534934</v>
+        <v>1441014074.814718</v>
       </c>
     </row>
     <row r="31">
@@ -2881,7 +3091,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1070873214.324934</v>
+        <v>1064540377.604717</v>
       </c>
     </row>
     <row r="33">
@@ -2901,7 +3111,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>107087321.4324934</v>
+        <v>106454037.7604717</v>
       </c>
     </row>
   </sheetData>
@@ -3988,7 +4198,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Based on 5-year projections</t>
+          <t>Based on 10-year projections</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4439,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7899.460189125347</v>
+        <v>5376.239870355783</v>
       </c>
     </row>
     <row r="3">
@@ -4240,7 +4450,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9307.284777286301</v>
+        <v>6334.381629429091</v>
       </c>
     </row>
     <row r="4">
@@ -4251,7 +4461,7 @@
         <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>10203.17315157054</v>
+        <v>6944.108203384832</v>
       </c>
     </row>
     <row r="5">
@@ -4262,7 +4472,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>11278.23920071163</v>
+        <v>7675.780092131721</v>
       </c>
     </row>
     <row r="6">
@@ -4273,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>14234.67083584964</v>
+        <v>9687.877786185671</v>
       </c>
     </row>
     <row r="7">
@@ -4284,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5605.421783722062</v>
+        <v>3480.52591025331</v>
       </c>
     </row>
     <row r="8">
@@ -4295,7 +4505,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>6368.536135466403</v>
+        <v>3954.359883183836</v>
       </c>
     </row>
     <row r="9">
@@ -4306,7 +4516,7 @@
         <v>2.5</v>
       </c>
       <c r="C9" t="n">
-        <v>6826.404746513005</v>
+        <v>4238.66026694215</v>
       </c>
     </row>
     <row r="10">
@@ -4317,7 +4527,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>7349.683159137698</v>
+        <v>4563.574991237368</v>
       </c>
     </row>
     <row r="11">
@@ -4328,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>8657.879190699423</v>
+        <v>5375.86180197541</v>
       </c>
     </row>
     <row r="12">
@@ -4339,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>4191.132911741099</v>
+        <v>2378.161370007988</v>
       </c>
     </row>
     <row r="13">
@@ -4350,7 +4560,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>4655.89220492427</v>
+        <v>2641.878274404914</v>
       </c>
     </row>
     <row r="14">
@@ -4361,7 +4571,7 @@
         <v>2.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4924.963374661895</v>
+        <v>2794.55648221366</v>
       </c>
     </row>
     <row r="15">
@@ -4372,7 +4582,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>5223.931341037035</v>
+        <v>2964.198935334489</v>
       </c>
     </row>
     <row r="16">
@@ -4383,7 +4593,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>5933.980261177992</v>
+        <v>3367.09976149646</v>
       </c>
     </row>
     <row r="17">
@@ -4394,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3245.985856552722</v>
+        <v>1685.863338848638</v>
       </c>
     </row>
     <row r="18">
@@ -4405,7 +4615,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>3551.301357911641</v>
+        <v>1844.434642997767</v>
       </c>
     </row>
     <row r="19">
@@ -4416,7 +4626,7 @@
         <v>2.5</v>
       </c>
       <c r="C19" t="n">
-        <v>3723.870989114508</v>
+        <v>1934.061901864666</v>
       </c>
     </row>
     <row r="20">
@@ -4427,7 +4637,7 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>3912.128768608546</v>
+        <v>2031.837093355829</v>
       </c>
     </row>
     <row r="21">
@@ -4438,7 +4648,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>4345.121661444832</v>
+        <v>2256.720033785504</v>
       </c>
     </row>
     <row r="22">
@@ -4449,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2578.891240166457</v>
+        <v>1227.843684780924</v>
       </c>
     </row>
     <row r="23">
@@ -4460,7 +4670,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>2790.455160859037</v>
+        <v>1328.572021014719</v>
       </c>
     </row>
     <row r="24">
@@ -4471,7 +4681,7 @@
         <v>2.5</v>
       </c>
       <c r="C24" t="n">
-        <v>2907.990672354915</v>
+        <v>1384.532207811273</v>
       </c>
     </row>
     <row r="25">
@@ -4482,7 +4692,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>3034.567377042784</v>
+        <v>1444.797024361407</v>
       </c>
     </row>
     <row r="26">
@@ -4493,7 +4703,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3319.364962590489</v>
+        <v>1580.392861599209</v>
       </c>
     </row>
   </sheetData>
